--- a/TestFiles/ExcelFiles/ASCPayment.xlsx
+++ b/TestFiles/ExcelFiles/ASCPayment.xlsx
@@ -77,7 +77,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="n">
-        <v>2.95</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="2">
@@ -85,7 +85,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>6.06</v>
+        <v>6.39</v>
       </c>
     </row>
   </sheetData>

--- a/TestFiles/ExcelFiles/ASCPayment.xlsx
+++ b/TestFiles/ExcelFiles/ASCPayment.xlsx
@@ -77,7 +77,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="n">
-        <v>5.16</v>
+        <v>11.85</v>
       </c>
     </row>
     <row r="2">
@@ -85,7 +85,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>6.17</v>
+        <v>8.13</v>
       </c>
     </row>
   </sheetData>
